--- a/test-files/разработка.xlsx
+++ b/test-files/разработка.xlsx
@@ -58,7 +58,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,14 +425,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,11 +464,26 @@
           <t>Дата приёма</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Телефон</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Стаж работы (лет)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Козлова Юлия Романовна</t>
+          <t>Петров Пётр Петрович</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,22 +493,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Поддержка</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>68233</v>
-      </c>
+          <t>Разработка</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07.07.2018</t>
-        </is>
+          <t>11.10.2018</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>petrov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>+72278248963</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Лебедев Сергей Александрович</t>
+          <t>Морозова Анастасия Олеговна</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -500,27 +529,40 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Аналитика</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>111024</v>
+        <v>164845</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18.02.2019</t>
-        </is>
+          <t>24.01.2023</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>morozova@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>+75098393010</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Сидорова Ольга Дмитриевна</t>
+          <t>Морозов Григорий Павлович</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Разработчик</t>
+          <t>Старший менеджер</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -529,187 +571,197 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>216640</v>
+        <v>191356</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03.02.2022</t>
-        </is>
+          <t>27.05.2024</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>morozov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>+77631165667</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Соколов Михаил Викторович</t>
+          <t>Новикова Дарья Викторовна</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Тимлид</t>
+          <t>Финансовый аналитик</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>104921</v>
-      </c>
+          <t>Разработка</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29.12.2020</t>
-        </is>
-      </c>
+          <t>24.03.2019</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>novikova@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>+77262473178</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Сидоров Алексей Николаевич</t>
+          <t>Козлова Юлия Романовна</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Специалист по продажам</t>
+          <t>UX-исследователь</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Поддержка</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>94862</v>
+        <v>272480</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.12.2023</t>
-        </is>
+          <t>23.07.2022</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>kozlova@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>+76026064746</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Лебедев Сергей Александрович</t>
+          <t>Новикова Дарья Викторовна</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Аналитик</t>
+          <t>Тестировщик</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Дизайн</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>149471</v>
+        <v>292177.34</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.01.2021</t>
-        </is>
-      </c>
+          <t>30.01.2024</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>+70978820812</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Лебедева Светлана Петровна</t>
+          <t>Сидоров Алексей Николаевич</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Старший аналитик</t>
+          <t>Финансовый аналитик</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Поддержка</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>135008</v>
+        <v>199336</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.08.2018</t>
-        </is>
+          <t>01.09.2024</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Лебедев Сергей Александрович</t>
+          <t>Смирнова Татьяна Николаевна</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Менеджер</t>
+          <t>Старший разработчик</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Финансы</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>155162</v>
+        <v>112570</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01.01.2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Сидоров Алексей Николаевич</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Старший аналитик</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>238196</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>12.07.2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Попов Андрей Дмитриевич</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>HR-специалист</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Продажи</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>153712</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>23.02.2023</t>
-        </is>
+          <t>21.06.2019</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>smirnova@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>+75107991183</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
